--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0175.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0175.xlsx
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Gần đây ta cứ nghe tin về một vụ việc lớn ở ga tàu. Ngươi có muốn đi kiểm tra không?</t>
+          <t>Gần đây tao cứ nghe tin về một vụ việc lớn ở ga tàu. Mày có muốn đi kiểm tra không?</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Đừng có lang thang nữa. Ta phải đưa con tuần lộc cơ khí về đã. Nghỉ ngơi chút đi, rồi mình đi tiếp.</t>
+          <t>Đừng có lang thang nữa. Tao phải đưa con tuần lộc cơ khí về đã. Nghỉ ngơi chút đi, rồi mình đi tiếp.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Tsk, được rồi, ngươi muốn gì? Để xem ta có thể tìm được không.</t>
+          <t>Tsk, được rồi, mày muốn gì? Để xem ta có thể tìm được không.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Đừng có mà bảo cậu chưa bao giờ thấy đồ ăn tử tế là như thế nào à?</t>
+          <t>Đừng có mà bảo mày chưa bao giờ thấy đồ ăn tử tế là như thế nào à?</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Ta có vài ý tưởng. Nhưng còn cậu thì sao? Không phải cậu đang nghiên cứu Reactor Drive vừa gặp sự cố lớn à?</t>
+          <t>Tao có vài ý tưởng. Nhưng còn cậu thì sao? Không phải cậu đang nghiên cứu Reactor Drive vừa gặp sự cố lớn à?</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Ta có vài ý tưởng. Nhưng còn cậu thì sao? Không phải cậu đang nghiên cứu Reactor Drive vừa gặp sự cố lớn à?</t>
+          <t>Tao có vài ý tưởng. Nhưng còn cậu thì sao? Không phải cậu đang nghiên cứu Reactor Drive vừa gặp sự cố lớn à?</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Ui, lộn xộn thế này. Ta vừa nghe tin có dữ liệu mới ở Đường Hầm Gào Thét, nhưng khi đến nơi thì đội nghiên cứu bảo là lỗi hệ thống.</t>
+          <t>Ui, lộn xộn thế này. Tao vừa nghe tin có dữ liệu mới ở Đường Hầm Gào Thét, nhưng khi đến nơi thì đội nghiên cứu bảo là lỗi hệ thống.</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Đợi đến khi ngươi nghe chuyện này! Tuần lộc cơ khí ăn cây cối rồi thải ra nguyên liệu thô, nên tụi ta gắn thêm cái thùng ở đằng sau. Để thu thập, hiểu chứ?</t>
+          <t>Đợi đến khi mày nghe chuyện này! Tuần lộc cơ khí ăn cây cối rồi thải ra nguyên liệu thô, nên tụi tao gắn thêm cái thùng ở đằng sau. Để thu thập, hiểu chứ?</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Thật sao? Cậu làm nó chạy được luôn không? Ta muốn xem cơ bắp nhân tạo của nó cử động.</t>
+          <t>Thật sao? Cậu làm nó chạy được luôn không? Tao muốn xem cơ bắp nhân tạo của nó cử động.</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Nói chuyện riêng à? Từ khi nào cậu với Dhalifa thân thiết thế?</t>
+          <t>Nói chuyện riêng à? Từ khi nào mày với Dhalifa thân thiết thế?</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Đừng hỏi thêm gì nữa. Ta đi một mình!</t>
+          <t>Đừng hỏi thêm gì nữa. Tao đi một mình!</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Thật sao? Ta cũng không rõ lắm. Mà bọn Sabercat Prowler cũng không phải dạng đó đâu.</t>
+          <t>Thật sao? Tao cũng không rõ lắm. Mà bọn Sabercat Prowler cũng không phải dạng đó đâu.</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Cảm ơn ta là đúng rồi. Ngươi sẽ làm được gì nếu thiếu ta chứ?</t>
+          <t>Cảm ơn tao là đúng rồi. Mày sẽ làm được gì nếu thiếu tao chứ?</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Ta đã thôi khóc từ lâu rồi, dù giờ đây ta thực sự cảm thấy hơi buồn... Ta luôn muốn đến nơi này, để xem nơi bố mẹ ta từng làm việc.</t>
+          <t>Tao đã thôi khóc từ lâu rồi, dù giờ đây tao thực sự cảm thấy hơi buồn... Tao luôn muốn đến nơi này, để xem nơi bố mẹ tao từng làm việc.</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Haha, làm sao ta khóc được nếu cậu cứ khóc hoài vậy?</t>
+          <t>Haha, làm sao tao khóc được nếu cậu cứ khóc hoài vậy?</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Thôi nói nhiều đi chụp ảnh giùm ta. Góc ánh sáng ở đây đẹp quá trời!</t>
+          <t>Thôi nói nhiều đi chụp ảnh giùm tao. Góc ánh sáng ở đây đẹp quá trời!</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Gì cơ? Xong rồi á? Ta đến trễ hả? Ta tưởng dự án còn tụt lùi xa cơ mà.</t>
+          <t>Gì cơ? Xong rồi á? Tao đến trễ hả? Tao tưởng dự án còn tụt lùi xa cơ mà.</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Lúc ta bận túi bụi ở Trạm Trung Chuyển thì ở đây đã xảy ra chuyện gì...</t>
+          <t>Lúc tao bận túi bụi ở Trạm Trung Chuyển thì ở đây đã xảy ra chuyện gì...</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Ngươi thậm chí còn chẳng nhấc nổi một ngón tay nếu không có chúng ta che chở, hiểu chưa?</t>
+          <t>Mày thậm chí còn chẳng nhấc nổi một ngón tay nếu không có chúng tao che chở, hiểu chưa?</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Tất nhiên, ta nhớ mà. Lúc ta còn nhỏ, nó vẫn thường cõng ta đi dạo quanh Rừng Bjartr.</t>
+          <t>Tất nhiên, ta nhớ mà. Lúc ta còn nhỏ, nó vẫn thường cõng ta đi dạo quanh Bjartr Woods.</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Và... giống như Dhalifa đã nói, ta bắt đầu hiểu tại sao cô ấy lại ở lại.</t>
+          <t>Và... giống như Dhalifa đã nói, tao bắt đầu hiểu tại sao cô ấy lại ở lại.</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Chuẩn không cần chỉnh, Ryan! Phần khóc thì để ta lo. (Nức nở)</t>
+          <t>Chuẩn không cần chỉnh, Ryan! Phần khóc thì để tao lo. (Nức nở)</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Lần tới ta đến đây sẽ là để tuyển người vào Đài Quan Sát, nên có khi chẳng còn thời gian đi lang thang nữa.</t>
+          <t>Lần tới tao đến đây sẽ là để tuyển người vào Đài Quan Sát, nên có khi chẳng còn thời gian đi lang thang nữa.</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Thật đấy! Con robot kia suýt nữa cho nổ tung cả ngọn đồi ngay trước mặt ta!</t>
+          <t>Thật đấy! Con robot kia suýt nữa cho nổ tung cả ngọn đồi ngay trước mặt tao!</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21699,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Ừ, đúng đấy. Có gì mà phải sợ chứ? Nếu sợ thì ta đã không có mặt ở đây rồi!</t>
+          <t>Ừ, đúng đấy. Có gì mà phải sợ chứ? Nếu sợ thì tao đã không có mặt ở đây rồi!</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Thiếu người à? Thôi được, tự mình lái vậy. Sao? Đường không ổn à? Thế thì đi xe máy của ta.</t>
+          <t>Thiếu người à? Thôi được, tự mình lái vậy. Sao? Đường không ổn à? Thế thì đi xe máy của tao.</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Hử? Cái này không phải lĩnh vực nghiên cứu của ta. Ta phải làm gì với nó đây?</t>
+          <t>Hử? Cái này không phải lĩnh vực nghiên cứu của tao. Tao phải làm gì với nó đây?</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Sau khi xong việc này, ta nghĩ cậu nợ ta một bữa tối đấy.</t>
+          <t>Sau khi xong việc này, tao nghĩ cậu nợ tao một bữa tối đấy.</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Tsk, cậu hiểu sai rồi. Nếu ta muốn làm mọi thứ theo sách vở, thì đã chẳng rời làng từ đầu.</t>
+          <t>Tsk, cậu hiểu sai rồi. Nếu tao muốn làm mọi thứ theo sách vở, thì đã chẳng rời làng từ đầu.</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Hồi đó hắn đã dẫn ta đi tham quan nơi này một lần. Ai tham gia dự án cũng đều đặt bao hy vọng vào những gì nơi này có thể làm cho Lahai-Roi.</t>
+          <t>Hồi đó hắn đã dẫn tao đi tham quan nơi này một lần. Ai tham gia dự án cũng đều đặt bao hy vọng vào những gì nơi này có thể làm cho Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Tin tốt nè! Ta thấy Dhalifa lén lau nước mắt khi nói chuyện với gia đình đấy!</t>
+          <t>Tin tốt nè! Tao thấy Dhalifa lén lau nước mắt khi nói chuyện với gia đình đấy!</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Tin tốt à? Ta hiểu ý ngươi.</t>
+          <t>Tin tốt à? Tao hiểu ý mày.</t>
         </is>
       </c>
     </row>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Ta có quen ngươi ở đâu không nhỉ?</t>
+          <t>Tao có quen mày ở đâu không nhỉ?</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Cao hơn nhiều so với nhìn từ dưới đất... Ui trời, lẽ ra ta không nên theo ngươi lên đây.</t>
+          <t>Cao hơn nhiều so với nhìn từ dưới đất... Ui trời, lẽ ra tao không nên theo mày lên đây.</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Ở Học viện Startorch, chúng tôi dùng khoa học để nói chuyện. Tỉnh lại đi hai đứa! Ta không tham gia trò này đâu.</t>
+          <t>Ở Học viện Startorch, chúng tôi dùng khoa học để nói chuyện. Tỉnh lại đi hai đứa! Tao không tham gia trò này đâu.</t>
         </is>
       </c>
     </row>
